--- a/exports/BAJAJHLDNG_full_report.xlsx
+++ b/exports/BAJAJHLDNG_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.94</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>5350</v>
+        <v>5148.05</v>
       </c>
       <c r="I2" t="n">
         <v>5303.16146965951</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>2.54</v>
+        <v>-1.33</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.49</v>
       </c>
       <c r="M2" t="n">
         <v>4.53</v>
       </c>
       <c r="N2" t="n">
-        <v>2.71</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
         <v>0.88</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>5110</v>
+        <v>5412.5</v>
       </c>
       <c r="I3" t="n">
         <v>5194.392441175321</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>67</v>
       </c>
       <c r="K3" t="n">
-        <v>0.74</v>
+        <v>-5.14</v>
       </c>
       <c r="L3" t="n">
-        <v>5.25</v>
+        <v>6.14</v>
       </c>
       <c r="M3" t="n">
         <v>2.94</v>
       </c>
       <c r="N3" t="n">
-        <v>2.93</v>
+        <v>5.19</v>
       </c>
       <c r="O3" t="n">
         <v>-4.3</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.27</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44663.55208333334</v>
+        <v>44664.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>5780.5</v>
+        <v>5611</v>
       </c>
       <c r="I4" t="n">
         <v>5619.878338675596</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>6.8</v>
+        <v>3.67</v>
       </c>
       <c r="L4" t="n">
         <v>7.07</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>14.46</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44748.38541666666</v>
+        <v>44748.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>4751.55</v>
+        <v>4776</v>
       </c>
       <c r="I5" t="n">
         <v>4775.045823112612</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>84</v>
+        <v>84.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>15.32</v>
+        <v>14.88</v>
       </c>
       <c r="L5" t="n">
         <v>4.79</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.31</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44833.38541666666</v>
+        <v>44833.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>6575</v>
+        <v>6378</v>
       </c>
       <c r="I6" t="n">
         <v>6562.167337769154</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>84.83333333333333</v>
+        <v>85</v>
       </c>
       <c r="K6" t="n">
-        <v>37.67</v>
+        <v>33.54</v>
       </c>
       <c r="L6" t="n">
         <v>1.14</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44874.38541666666</v>
+        <v>44874.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>6795</v>
+        <v>6890</v>
       </c>
       <c r="I7" t="n">
         <v>6820.83217680793</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>40.83333333333334</v>
+        <v>41</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.54</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>7.95</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M7" t="n">
         <v>1.57</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>4.76</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>6578</v>
+        <v>6532.45</v>
       </c>
       <c r="I8" t="n">
         <v>6561.701187789766</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.53</v>
+        <v>-5.19</v>
       </c>
       <c r="L8" t="n">
-        <v>4.79</v>
+        <v>5.53</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>5.98</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>6284.5</v>
+        <v>6590</v>
       </c>
       <c r="I9" t="n">
         <v>6510.644700648214</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>-0.88</v>
       </c>
       <c r="L9" t="n">
         <v>2.12</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>13.28</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>6101</v>
+        <v>5930.8</v>
       </c>
       <c r="I10" t="n">
         <v>5961.6015993008</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.42</v>
+        <v>-10</v>
       </c>
       <c r="L10" t="n">
-        <v>8.859999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="M10" t="n">
         <v>4.84</v>
       </c>
       <c r="N10" t="n">
-        <v>4.26</v>
+        <v>5.64</v>
       </c>
       <c r="O10" t="n">
         <v>9.380000000000001</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.5</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44939.38541666666</v>
+        <v>44939.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>5863.45</v>
+        <v>5910</v>
       </c>
       <c r="I11" t="n">
         <v>5906.462915747385</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>1.14</v>
+        <v>0.35</v>
       </c>
       <c r="L11" t="n">
         <v>3.36</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>4.5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44943.55208333334</v>
+        <v>44944.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>5720</v>
+        <v>5635.05</v>
       </c>
       <c r="I12" t="n">
         <v>5644.324655132243</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.21</v>
+        <v>-4.65</v>
       </c>
       <c r="L12" t="n">
-        <v>4.3</v>
+        <v>5.21</v>
       </c>
       <c r="M12" t="n">
         <v>-0</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.06</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44953.38541666666</v>
+        <v>44953.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>5778.55</v>
+        <v>5900</v>
       </c>
       <c r="I13" t="n">
         <v>5860.288666879417</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.55</v>
+        <v>-4.7</v>
       </c>
       <c r="L13" t="n">
-        <v>4.92</v>
+        <v>5.5</v>
       </c>
       <c r="M13" t="n">
         <v>0.57</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.81</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45002.38541666666</v>
+        <v>45002.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>6126.85</v>
+        <v>5989</v>
       </c>
       <c r="I14" t="n">
         <v>5998.805586182086</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>48.83333333333334</v>
+        <v>49</v>
       </c>
       <c r="K14" t="n">
-        <v>3.84</v>
+        <v>1.51</v>
       </c>
       <c r="L14" t="n">
         <v>2.69</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>7.25</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45033.55208333334</v>
+        <v>45034.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>6110</v>
+        <v>6411.95</v>
       </c>
       <c r="I15" t="n">
         <v>6160.135976478558</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.02</v>
+        <v>-7.06</v>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>11.04</v>
       </c>
       <c r="M15" t="n">
         <v>2.08</v>
       </c>
       <c r="N15" t="n">
-        <v>2.64</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
         <v>-1.85</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7.09</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45062.38541666666</v>
+        <v>45062.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>6656.6</v>
+        <v>6615</v>
       </c>
       <c r="I16" t="n">
         <v>6654.956769046275</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>3.82</v>
+        <v>3.17</v>
       </c>
       <c r="L16" t="n">
         <v>4.91</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>4.41</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45069.38541666666</v>
+        <v>45069.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>6578.95</v>
+        <v>6661.1</v>
       </c>
       <c r="I17" t="n">
         <v>6607.411497205881</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.54</v>
+        <v>-0.7</v>
       </c>
       <c r="L17" t="n">
-        <v>0.74</v>
+        <v>0.98</v>
       </c>
       <c r="M17" t="n">
         <v>0.95</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.27</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45085.38541666666</v>
+        <v>45085.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>6929.95</v>
+        <v>6830</v>
       </c>
       <c r="I18" t="n">
         <v>6845.891174586423</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K18" t="n">
-        <v>4.04</v>
+        <v>2.54</v>
       </c>
       <c r="L18" t="n">
         <v>1.29</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.09</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45110.55208333334</v>
+        <v>45111.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>6980</v>
+        <v>7169.45</v>
       </c>
       <c r="I19" t="n">
         <v>7078.036546455829</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.2</v>
+        <v>-4.97</v>
       </c>
       <c r="L19" t="n">
-        <v>3.72</v>
+        <v>6.08</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.38</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45149.38541666666</v>
+        <v>45149.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>7392.9</v>
+        <v>7227.05</v>
       </c>
       <c r="I20" t="n">
         <v>7281.089997951684</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>3.12</v>
+        <v>0.8</v>
       </c>
       <c r="L20" t="n">
         <v>2.41</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45167.55208333334</v>
+        <v>45168.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>7360</v>
+        <v>7401</v>
       </c>
       <c r="I21" t="n">
         <v>7366.459059256527</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.84</v>
+        <v>-2.41</v>
       </c>
       <c r="L21" t="n">
         <v>2.81</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>3.75</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45173.55208333334</v>
+        <v>45174.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>7226</v>
+        <v>7175</v>
       </c>
       <c r="I22" t="n">
         <v>7206.330402570351</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.36</v>
+        <v>-3.05</v>
       </c>
       <c r="L22" t="n">
-        <v>2.68</v>
+        <v>3.51</v>
       </c>
       <c r="M22" t="n">
         <v>0.13</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.21</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45189.55208333334</v>
+        <v>45190.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>7250</v>
+        <v>7365</v>
       </c>
       <c r="I23" t="n">
         <v>7316.871317761286</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.05</v>
+        <v>-2.65</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>2.93</v>
       </c>
       <c r="M23" t="n">
         <v>0.75</v>
       </c>
       <c r="N23" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="O23" t="n">
         <v>-0.77</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>4.12</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45197.38541666666</v>
+        <v>45197.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>7194.3</v>
+        <v>7070</v>
       </c>
       <c r="I24" t="n">
         <v>7124.541854588856</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.32</v>
+        <v>-4.01</v>
       </c>
       <c r="L24" t="n">
-        <v>3.12</v>
+        <v>4.68</v>
       </c>
       <c r="M24" t="n">
         <v>0.33</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.2</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45219.38541666666</v>
+        <v>45219.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>6963.9</v>
+        <v>7037.95</v>
       </c>
       <c r="I25" t="n">
         <v>7030.72134399779</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21.83333333333333</v>
+        <v>22</v>
       </c>
       <c r="K25" t="n">
-        <v>1.5</v>
+        <v>0.45</v>
       </c>
       <c r="L25" t="n">
         <v>2.02</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>4.62</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45225.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>6834.35</v>
+        <v>6675.05</v>
       </c>
       <c r="I26" t="n">
         <v>6798.13808569682</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.89</v>
+        <v>-5.16</v>
       </c>
       <c r="L26" t="n">
-        <v>3.38</v>
+        <v>5.19</v>
       </c>
       <c r="M26" t="n">
-        <v>-0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>3.44</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45236.55208333334</v>
+        <v>45237.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>7000</v>
+        <v>7050</v>
       </c>
       <c r="I27" t="n">
         <v>7031.901797026885</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.87</v>
+        <v>-5.62</v>
       </c>
       <c r="L27" t="n">
-        <v>5.38</v>
+        <v>6.33</v>
       </c>
       <c r="M27" t="n">
         <v>1.75</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.58</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45288.38541666666</v>
+        <v>45288.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>7932.2</v>
+        <v>7715</v>
       </c>
       <c r="I28" t="n">
         <v>7720.148588781287</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>12.51</v>
+        <v>9.43</v>
       </c>
       <c r="L28" t="n">
         <v>0.71</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45295.38541666666</v>
+        <v>45295.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>8097.25</v>
+        <v>8200</v>
       </c>
       <c r="I29" t="n">
         <v>8143.640767455794</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.95</v>
+        <v>-6.29</v>
       </c>
       <c r="L29" t="n">
-        <v>6.55</v>
+        <v>6.88</v>
       </c>
       <c r="M29" t="n">
         <v>1.64</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.37</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>8589</v>
+        <v>8475.1</v>
       </c>
       <c r="I30" t="n">
         <v>8522.77174000233</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>68</v>
+        <v>68.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>4.74</v>
+        <v>3.35</v>
       </c>
       <c r="L30" t="n">
         <v>3.78</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.8</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45404.55208333334</v>
+        <v>45405.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>7960</v>
+        <v>8177.1</v>
       </c>
       <c r="I31" t="n">
         <v>8144.729020335874</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K31" t="n">
-        <v>6.08</v>
+        <v>3.52</v>
       </c>
       <c r="L31" t="n">
         <v>1.25</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.36</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45433.55208333334</v>
+        <v>45434.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>8148</v>
+        <v>8101.5</v>
       </c>
       <c r="I32" t="n">
         <v>8114.709523780039</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.36</v>
+        <v>-0.92</v>
       </c>
       <c r="L32" t="n">
         <v>2.56</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>4.54</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45447.55208333334</v>
+        <v>45448.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>7875</v>
+        <v>8065</v>
       </c>
       <c r="I33" t="n">
         <v>8046.711217661807</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>2.8</v>
+        <v>0.45</v>
       </c>
       <c r="L33" t="n">
         <v>1.2</v>
@@ -2322,7 +2717,7 @@
         <v>2.06</v>
       </c>
       <c r="N33" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="O33" t="n">
         <v>-0.28</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.21</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45506.38541666666</v>
+        <v>45506.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>9523</v>
+        <v>9380.5</v>
       </c>
       <c r="I34" t="n">
         <v>9385.366478121021</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>58</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="K34" t="n">
-        <v>18.08</v>
+        <v>16.31</v>
       </c>
       <c r="L34" t="n">
         <v>2.05</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.87</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45523.55208333334</v>
+        <v>45524.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>9610</v>
+        <v>9740.35</v>
       </c>
       <c r="I35" t="n">
         <v>9724.299143228875</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.45</v>
+        <v>-3.84</v>
       </c>
       <c r="L35" t="n">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="M35" t="n">
         <v>1.18</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.36</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45569.38541666666</v>
+        <v>45569.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>10400.05</v>
+        <v>10320</v>
       </c>
       <c r="I36" t="n">
         <v>10323.52081414602</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K36" t="n">
-        <v>6.77</v>
+        <v>5.95</v>
       </c>
       <c r="L36" t="n">
         <v>1.48</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.38</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45607.38541666666</v>
+        <v>45607.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>10729.3</v>
+        <v>10822.55</v>
       </c>
       <c r="I37" t="n">
         <v>10771.5640505035</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>37.83333333333334</v>
+        <v>38</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.97</v>
+        <v>-4.87</v>
       </c>
       <c r="L37" t="n">
-        <v>5.59</v>
+        <v>5.6</v>
       </c>
       <c r="M37" t="n">
         <v>1.73</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.73</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45667.38541666666</v>
+        <v>45667.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>11025</v>
+        <v>10830</v>
       </c>
       <c r="I38" t="n">
         <v>10946.12590335467</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>59.83333333333334</v>
+        <v>60</v>
       </c>
       <c r="K38" t="n">
-        <v>1.87</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L38" t="n">
         <v>6.49</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>10.07</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45686.38541666666</v>
+        <v>45686.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>11275.9</v>
+        <v>11476.35</v>
       </c>
       <c r="I39" t="n">
         <v>11403.28668261302</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.12</v>
+        <v>-5.97</v>
       </c>
       <c r="L39" t="n">
-        <v>5.48</v>
+        <v>6.17</v>
       </c>
       <c r="M39" t="n">
         <v>2.39</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>6.99</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45719.55208333334</v>
+        <v>45720.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>11350</v>
+        <v>11232.75</v>
       </c>
       <c r="I40" t="n">
         <v>11279.5391186285</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.1</v>
+        <v>-2.12</v>
       </c>
       <c r="L40" t="n">
-        <v>3.23</v>
+        <v>3.43</v>
       </c>
       <c r="M40" t="n">
         <v>1.34</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>11.3</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45737.38541666666</v>
+        <v>45737.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>12182</v>
+        <v>12324</v>
       </c>
       <c r="I41" t="n">
         <v>12300.18518140984</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.449999999999999</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>9.68</v>
+        <v>10.3</v>
       </c>
       <c r="M41" t="n">
         <v>1.46</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>7.02</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>11909.95</v>
+        <v>11495</v>
       </c>
       <c r="I42" t="n">
         <v>11862.30856572034</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.36</v>
+        <v>-6.73</v>
       </c>
       <c r="L42" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0.03</v>
+        <v>3.44</v>
       </c>
       <c r="N42" t="n">
         <v>4.58</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>11609</v>
+        <v>11931</v>
       </c>
       <c r="I43" t="n">
         <v>11797.63004654874</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.99</v>
+        <v>-3.79</v>
       </c>
       <c r="L43" t="n">
-        <v>3.44</v>
+        <v>4.54</v>
       </c>
       <c r="M43" t="n">
         <v>3.69</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.94</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>11755</v>
+        <v>11442</v>
       </c>
       <c r="I44" t="n">
         <v>11647.04193973793</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.48</v>
+        <v>-4.1</v>
       </c>
       <c r="L44" t="n">
-        <v>3.59</v>
+        <v>4.36</v>
       </c>
       <c r="M44" t="n">
         <v>0.92</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.26</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45791.38541666666</v>
+        <v>45791.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>12038</v>
+        <v>12069</v>
       </c>
       <c r="I45" t="n">
         <v>12046.89933314197</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.21</v>
+        <v>-5.48</v>
       </c>
       <c r="L45" t="n">
         <v>6.54</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.18</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45827.38541666666</v>
+        <v>45827.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>13529</v>
+        <v>13487</v>
       </c>
       <c r="I46" t="n">
         <v>13494.51693349546</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K46" t="n">
-        <v>12.1</v>
+        <v>11.75</v>
       </c>
       <c r="L46" t="n">
         <v>0.97</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.17</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45835.55208333334</v>
+        <v>45838.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>14134</v>
+        <v>14207</v>
       </c>
       <c r="I47" t="n">
         <v>14183.45503561948</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.8</v>
+        <v>-5.34</v>
       </c>
       <c r="L47" t="n">
         <v>6.77</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.16</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45891.38541666666</v>
+        <v>45891.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>13651</v>
+        <v>13500</v>
       </c>
       <c r="I48" t="n">
         <v>13638.03852847759</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.91</v>
+        <v>-4.98</v>
       </c>
       <c r="L48" t="n">
         <v>5.65</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.52</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45915.55208333334</v>
+        <v>45916.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>13155</v>
+        <v>13286</v>
       </c>
       <c r="I49" t="n">
         <v>13277.85449828607</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>2.56</v>
+        <v>1.59</v>
       </c>
       <c r="L49" t="n">
         <v>1.16</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>4.31</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>13200</v>
+        <v>12923</v>
       </c>
       <c r="I50" t="n">
         <v>13108.43389662564</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.65</v>
+        <v>-2.73</v>
       </c>
       <c r="L50" t="n">
-        <v>1.08</v>
+        <v>2.87</v>
       </c>
       <c r="M50" t="n">
         <v>0.39</v>
       </c>
       <c r="N50" t="n">
-        <v>1.41</v>
+        <v>2.31</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.37</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>12170</v>
+        <v>12520</v>
       </c>
       <c r="I51" t="n">
         <v>12510.17535257035</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K51" t="n">
-        <v>5.83</v>
+        <v>3.12</v>
       </c>
       <c r="L51" t="n">
         <v>2.63</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.46</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45959.55208333334</v>
+        <v>45960.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>12615</v>
+        <v>12378</v>
       </c>
       <c r="I52" t="n">
         <v>12512.53334606636</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K52" t="n">
-        <v>0.76</v>
+        <v>-1.13</v>
       </c>
       <c r="L52" t="n">
         <v>2.42</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.18</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>12080</v>
+        <v>13105</v>
       </c>
       <c r="I53" t="n">
         <v>12667.20864260117</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K53" t="n">
-        <v>2.41</v>
+        <v>-5.87</v>
       </c>
       <c r="L53" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="M53" t="n">
         <v>0.67</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O53" t="n">
         <v>-1.25</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.92</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45971.55208333334</v>
+        <v>45972.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>12580</v>
+        <v>12192</v>
       </c>
       <c r="I54" t="n">
         <v>12224.27275958937</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.01</v>
+        <v>-6.97</v>
       </c>
       <c r="L54" t="n">
         <v>8.32</v>
@@ -3519,7 +4166,7 @@
         <v>0.54</v>
       </c>
       <c r="N54" t="n">
-        <v>3.22</v>
+        <v>3.46</v>
       </c>
       <c r="O54" t="n">
         <v>8.199999999999999</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.09</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46021.55208333334</v>
+        <v>46022.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>11024</v>
+        <v>11403</v>
       </c>
       <c r="I55" t="n">
         <v>11397.10957097547</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K55" t="n">
-        <v>9.58</v>
+        <v>6.47</v>
       </c>
       <c r="L55" t="n">
         <v>6.33</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.37</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>11060</v>
+        <v>10788</v>
       </c>
       <c r="I56" t="n">
         <v>10823.59972220026</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.01</v>
+        <v>-5.39</v>
       </c>
       <c r="L56" t="n">
-        <v>3.39</v>
+        <v>6.69</v>
       </c>
       <c r="M56" t="n">
         <v>0.04</v>
       </c>
       <c r="N56" t="n">
-        <v>1.19</v>
+        <v>2.98</v>
       </c>
       <c r="O56" t="n">
         <v>2.55</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.95</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>10911</v>
+        <v>11025</v>
       </c>
       <c r="I57" t="n">
         <v>10998.34427182295</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.14</v>
+        <v>-2.2</v>
       </c>
       <c r="L57" t="n">
         <v>3.46</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.78</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46078.55208333334</v>
+        <v>46079.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>11140</v>
+        <v>10893</v>
       </c>
       <c r="I58" t="n">
         <v>10938.28691085248</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>1.04</v>
+        <v>-1.2</v>
       </c>
       <c r="L58" t="n">
         <v>3.17</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.17</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>9297.5</v>
+        <v>9955</v>
       </c>
       <c r="I59" t="n">
         <v>9412.7783408416</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K59" t="n">
-        <v>14.65</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L59" t="n">
         <v>3.04</v>
@@ -3804,7 +4511,7 @@
         <v>2.82</v>
       </c>
       <c r="N59" t="n">
-        <v>2.49</v>
+        <v>7.56</v>
       </c>
       <c r="O59" t="n">
         <v>-2.15</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>10.26</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>10265</v>
+        <v>10100</v>
       </c>
       <c r="I60" t="n">
         <v>10101.55047023378</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>3.11</v>
+        <v>1.46</v>
       </c>
       <c r="L60" t="n">
         <v>5.07</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>7.38</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46167.55208333334</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>10630</v>
+        <v>10747</v>
       </c>
       <c r="I61" t="n">
         <v>10702.40330971985</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.25</v>
+        <v>-6.41</v>
       </c>
       <c r="L61" t="n">
-        <v>6.35</v>
+        <v>8.23</v>
       </c>
       <c r="M61" t="n">
         <v>1.43</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.85</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46177.38541666666</v>
+        <v>46177.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>10200</v>
+        <v>10081</v>
       </c>
       <c r="I62" t="n">
         <v>10118.358417844</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>-5.09</v>
+        <v>-6.2</v>
       </c>
       <c r="L62" t="n">
         <v>6.39</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>5.95</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>10156</v>
+        <v>10429</v>
       </c>
       <c r="I63" t="n">
         <v>10406.97035053033</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.74</v>
+        <v>-3.45</v>
       </c>
       <c r="L63" t="n">
-        <v>2.72</v>
+        <v>4.67</v>
       </c>
       <c r="M63" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="N63" t="n">
         <v>4.02</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.04</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>10586</v>
+        <v>10385</v>
       </c>
       <c r="I64" t="n">
         <v>10476.83983036176</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>1.51</v>
+        <v>-0.42</v>
       </c>
       <c r="L64" t="n">
         <v>1.68</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.42</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46230.55208333334</v>
+        <v>46231.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>10735</v>
+        <v>10801</v>
       </c>
       <c r="I65" t="n">
         <v>10798.22198635627</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.37</v>
+        <v>-4.01</v>
       </c>
       <c r="L65" t="n">
         <v>5.1</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>4.19</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46258.38541666666</v>
+        <v>46258.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>11214</v>
+        <v>11050</v>
       </c>
       <c r="I66" t="n">
         <v>11050.48077132511</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>3.82</v>
+        <v>2.31</v>
       </c>
       <c r="L66" t="n">
         <v>0.5600000000000001</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.47</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46283.55208333334</v>
+        <v>46286.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>11299</v>
+        <v>11391</v>
       </c>
       <c r="I67" t="n">
         <v>11371.3791253757</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>25</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.25</v>
+        <v>-3.09</v>
       </c>
       <c r="L67" t="n">
         <v>4.25</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>4.63</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46289.38541666666</v>
+        <v>46289.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>11145</v>
+        <v>10919</v>
       </c>
       <c r="I68" t="n">
         <v>10943.57776673121</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.16</v>
+        <v>-4.14</v>
       </c>
       <c r="L68" t="n">
-        <v>2.53</v>
+        <v>4.33</v>
       </c>
       <c r="M68" t="n">
         <v>0.8100000000000001</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>5.71</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>10770</v>
+        <v>11181</v>
       </c>
       <c r="I69" t="n">
         <v>11009.66711121744</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>1.36</v>
+        <v>-2.4</v>
       </c>
       <c r="L69" t="n">
-        <v>2.17</v>
+        <v>2.76</v>
       </c>
       <c r="M69" t="n">
         <v>0.82</v>
       </c>
       <c r="N69" t="n">
-        <v>1.87</v>
+        <v>4.22</v>
       </c>
       <c r="O69" t="n">
         <v>-4.26</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>7.67</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46323.38541666666</v>
+        <v>46323.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>10695</v>
+        <v>10520</v>
       </c>
       <c r="I70" t="n">
         <v>10682.21659107988</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.35</v>
+        <v>-5.91</v>
       </c>
       <c r="L70" t="n">
-        <v>4.59</v>
+        <v>6.21</v>
       </c>
       <c r="M70" t="n">
         <v>0.6899999999999999</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>1</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.7</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84.8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="11">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.09</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.17</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.01</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>37.67</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.74</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.36</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7610,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.68</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="25">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.21</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="27">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
